--- a/hardware/docs/output/BOM_OZDISAN_REV_C_20260921.xlsx
+++ b/hardware/docs/output/BOM_OZDISAN_REV_C_20260921.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Ozet" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM_Ozdisan'!$A$1:$S$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM_Ozdisan'!$A$1:$S$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S74"/>
+  <dimension ref="A1:S71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1057,7 +1057,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U10</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1065,80 +1065,50 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TPS61023DRLR</t>
+          <t>TPD4EUSB30</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>DRL-6</t>
+          <t>USON-10</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>TPS61023DRLR</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>RT4812GJ8F</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>RICHTEK</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Senkron boost 1,8–5,5V giriş/çıkış, 2,1A, TSOT-23-8</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>614996</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>308</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>15.1267</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>15.13</v>
-      </c>
-      <c r="P8" s="7" t="inlineStr">
-        <is>
-          <t>Muadil</t>
+          <t>TPD4EUSB30</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>Stokta yok</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Yeni seçildi</t>
+          <t>Tasarım MPN'i</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21.09 üçüncü tur: TPS61023 stokta yok. RT4812 özellik muadili: senkron boost, VIN 1,8–5,5V, VOUT 1,8–5,5V, ortalama çıkış akım sınırı 1A/2,1A (ILIM pini), gerçek yük ayırma, VFB 0,5V, fsw ~0,5 MHz. Backlight yükü (≤200 mA, 4,19V) için yeterli. Değişmesi gerekenler: footprint (TSOT-23-8), FB bölücü 0,5V referansa göre (ör. R44=732k / R45=100k → 4,16V; CAT4104 payı korunur), bobin RT4812 datasheet'ine göre (1,5–2,2 µH), ILIM pini L'ye bağlanır. Alternatif: TPS63020DSJR buck-boost (103 stok, VSON-14).</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>https://www.ozdisan.com/p/dc-dc-voltaj-regulatorleri-275/richtek-rt4812gj8f-614996</t>
-        </is>
-      </c>
+          <t>Stokta yok. Stoktaki TPD4E1U06DBVR / TPD4E001DBVR SOT-23-6 kılıflı; kullanmak footprint değişikliği gerektirir.</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1146,32 +1116,58 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CAT4104V-GT3</t>
+          <t>TPS55340PWPR</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SOIC-8</t>
+          <t>HTSSOP-14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>CAT4104V-GT3</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="4" t="inlineStr">
-        <is>
-          <t>Stokta yok</t>
+          <t>TPS55340PWPR</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>TPS55340PWPR</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>TEXAS</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>IC-55340 REG BOOST ADJ 5.25A 14HTSSOP</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>645605</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>449</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>96.1498</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1179,17 +1175,17 @@
           <t>Tasarım MPN'i</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>Özdisan indeksinde bulunamadı.</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="n"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ozdisan.com/p/dc-dc-voltaj-regulatorleri-275/texas-tps55340pwpr-645605</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U12</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1197,17 +1193,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TPD4EUSB30</t>
+          <t>AP74502Q</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>USON-10</t>
+          <t>TSOT-23-8</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>TPD4EUSB30</t>
+          <t>AP74502Q</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
@@ -1232,7 +1228,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Stokta yok. Stoktaki TPD4E1U06DBVR / TPD4E001DBVR SOT-23-6 kılıflı; kullanmak footprint değişikliği gerektirir.</t>
+          <t>İdeal diyot kategorisi indekste; parça yok. Stokta yalnız LM74610/LM74801/TPS2115 var (farklı kılıf/işlev).</t>
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
@@ -1240,62 +1236,62 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>Q1,Q2</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TPS55340PWPR</t>
+          <t>BSS138</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>HTSSOP-14</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>TPS55340PWPR</t>
+          <t>BSS138</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>TPS55340PWPR</t>
+          <t>BSS138P,215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>TEXAS</t>
+          <t>NEXPERIA</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>IC-55340 REG BOOST ADJ 5.25A 14HTSSOP</t>
+          <t>MOSFET 360mA 60V N-CH SOT23</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>645605</v>
+        <v>737689</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>449</v>
+        <v>73553</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>96.1498</v>
+        <v>2.25609</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>96.15000000000001</v>
+        <v>11.28</v>
       </c>
       <c r="P11" s="5" t="inlineStr">
         <is>
@@ -1304,126 +1300,160 @@
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Tasarım MPN'i</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr"/>
+          <t>Yeni seçildi</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>Jenerik BSS138 karşılığı; 60V / 360mA, SOT-23 G-S-D.</t>
+        </is>
+      </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/dc-dc-voltaj-regulatorleri-275/texas-tps55340pwpr-645605</t>
+          <t>https://www.ozdisan.com/p/discrete-mosfetler-435/nexperia-bss138p-215-737689</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>Q3,Q5</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AP74502Q</t>
+          <t>SQJB60EP</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>TSOT-23-8</t>
+          <t>PowerPAK SO-8L Dual</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>AP74502Q</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
-      <c r="P12" s="4" t="inlineStr">
-        <is>
-          <t>Stokta yok</t>
+          <t>SQJB60EP-T1_GE3</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>SQJB60EP-T1_GE3</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>VISHAY SILICONIX</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>MOSFET 30A 60V N-CH POWERPAK SO-8</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>700940</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>107664</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>38.5753</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>77.15000000000001</v>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Tasarım MPN'i</t>
+          <t>Önceden seçilmiş</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>İdeal diyot kategorisi indekste; parça yok. Stokta yalnız LM74610/LM74801/TPS2115 var (farklı kılıf/işlev).</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="n"/>
+          <t>Seçim raporu: design_decisions/reports/sqjb60ep-20260921. Footprint henüz atanmamış.</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ozdisan.com/p/discrete-mosfetler-435/vishay-siliconix-sqjb60ep-t1-ge3-700940</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Q1,Q2</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>SS2060FL</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>SOD-123F</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>SS2060FL_R1_00001</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SS2060FL_R1_00001</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>PANJIT</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>SCHOTTKY 2A 60V SOD123FL</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>574723</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>51111</v>
+      </c>
+      <c r="K13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>BSS138</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>SOT-23</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>BSS138</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>BSS138P,215</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>NEXPERIA</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>MOSFET 360mA 60V N-CH SOT23</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>737689</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>73553</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="L13" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>2.25609</v>
+        <v>2.88212</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>11.28</v>
+        <v>5.76</v>
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
@@ -1432,24 +1462,20 @@
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Yeni seçildi</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>Jenerik BSS138 karşılığı; 60V / 360mA, SOT-23 G-S-D.</t>
-        </is>
-      </c>
+          <t>Önceden seçilmiş</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/discrete-mosfetler-435/nexperia-bss138p-215-737689</t>
+          <t>https://www.ozdisan.com/p/schottky-diyotlar-385/panjit-ss2060fl-r1-00001-574723</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Q3,Q5</t>
+          <t>D3,D7</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1457,54 +1483,54 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SQJB60EP</t>
+          <t>SMBJ30A</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>PowerPAK SO-8L Dual</t>
+          <t>SMB (DO-214AA)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>SQJB60EP-T1_GE3</t>
+          <t>SMBJ30A</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>SQJB60EP-T1_GE3</t>
+          <t>SMBJ30A-E3/52</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>VISHAY SILICONIX</t>
+          <t>VISHAY</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>MOSFET 30A 60V N-CH POWERPAK SO-8</t>
+          <t>TVS 600W 30V SMB Uni</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>700940</v>
+        <v>507320</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>107664</v>
+        <v>15956</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>38.5753</v>
+        <v>4.31596</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>77.15000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="P14" s="5" t="inlineStr">
         <is>
@@ -1513,24 +1539,24 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Önceden seçilmiş</t>
+          <t>Yeni seçildi</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Seçim raporu: design_decisions/reports/sqjb60ep-20260921. Footprint henüz atanmamış.</t>
+          <t>Şema açıklaması '400W / SMA' diyor ama footprint SMB; SMB/600W parça footprint'e uyar.</t>
         </is>
       </c>
       <c r="S14" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/discrete-mosfetler-435/vishay-siliconix-sqjb60ep-t1-ge3-700940</t>
+          <t>https://www.ozdisan.com/p/tvs-diyotlar-386/vishay-smbj30a-e3-52-507320</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1538,22 +1564,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SS2060FL</t>
+          <t>SS34 TBD</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>SOD-123F</t>
+          <t>SMA (DO-214AC)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>SS2060FL_R1_00001</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>SS2060FL_R1_00001</t>
+          <t>SX36_R1_00001</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1563,14 +1589,14 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SCHOTTKY 2A 60V SOD123FL</t>
+          <t>SCHOTTKY 3A 60V SMA</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>574723</v>
+        <v>574842</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>51111</v>
+        <v>437</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>2</v>
@@ -1582,10 +1608,10 @@
         <v>2</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>2.88212</v>
+        <v>4.5201</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>5.76</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="P15" s="5" t="inlineStr">
         <is>
@@ -1594,75 +1620,79 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Önceden seçilmiş</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr"/>
+          <t>Yeni seçildi</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>SS34 Özdisan'da yalnız SMC kılıfta var. SMA'da 3A/60V seçildi (V_PRE ~28V için pay). Alternatifler: MBRA340T3G 40V (191 stok), BX310 100V (19411 stok).</t>
+        </is>
+      </c>
       <c r="S15" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/schottky-diyotlar-385/panjit-ss2060fl-r1-00001-574723</t>
+          <t>https://www.ozdisan.com/p/schottky-diyotlar-385/panjit-sx36-r1-00001-574842</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>D3,D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SMBJ30A</t>
+          <t>BAT54</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SMB (DO-214AA)</t>
+          <t>SOD-123</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>SMBJ30A</t>
+          <t>BAT54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>SMBJ30A-E3/52</t>
+          <t>BAT54T1G</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>VISHAY</t>
+          <t>ONS</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>TVS 600W 30V SMB Uni</t>
+          <t>SCHOTTKY 200mA 30V SOD123 Single</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>507320</v>
+        <v>614028</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15956</v>
+        <v>595</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>4.31596</v>
+        <v>1.42727</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>8.630000000000001</v>
+        <v>7.14</v>
       </c>
       <c r="P16" s="5" t="inlineStr">
         <is>
@@ -1676,19 +1706,19 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>Şema açıklaması '400W / SMA' diyor ama footprint SMB; SMB/600W parça footprint'e uyar.</t>
+          <t>Otomatik MPN eşleşmesi BAT54A (çift, SOT-23) getirdi; footprint'e uyan tekli SOD-123 seçildi.</t>
         </is>
       </c>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/tvs-diyotlar-386/vishay-smbj30a-e3-52-507320</t>
+          <t>https://www.ozdisan.com/p/schottky-diyotlar-385/ons-bat54t1g-614028</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1696,22 +1726,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SS34 TBD</t>
+          <t>BZT52C12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>SMA (DO-214AC)</t>
+          <t>SOD-123</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BZT52C12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>SX36_R1_00001</t>
+          <t>BZT52-C12_R1_00001</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1721,29 +1751,29 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SCHOTTKY 3A 60V SMA</t>
+          <t>ZENER 410mW 12V SOD123 5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>574842</v>
+        <v>560765</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>437</v>
+        <v>4720</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>4.5201</v>
+        <v>1.11884</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>9.039999999999999</v>
+        <v>5.59</v>
       </c>
       <c r="P17" s="5" t="inlineStr">
         <is>
@@ -1755,21 +1785,17 @@
           <t>Yeni seçildi</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>SS34 Özdisan'da yalnız SMC kılıfta var. SMA'da 3A/60V seçildi (V_PRE ~28V için pay). Alternatifler: MBRA340T3G 40V (191 stok), BX310 100V (19411 stok).</t>
-        </is>
-      </c>
+      <c r="R17" s="2" t="inlineStr"/>
       <c r="S17" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/schottky-diyotlar-385/panjit-sx36-r1-00001-574842</t>
+          <t>https://www.ozdisan.com/p/zener-diyotlar-390/panjit-bzt52-c12-r1-00001-560765</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1777,54 +1803,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>BAT54</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>SOD-123</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>BAT54</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>BAT54T1G</t>
+          <t>APHHS1005SURCK</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ONS</t>
+          <t>KINGBRIGHT</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SCHOTTKY 200mA 30V SOD123 Single</t>
+          <t>LED SMD 0402 RED 630nm 220mcd</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>614028</v>
+        <v>708179</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>595</v>
+        <v>272</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.42727</v>
+        <v>18.1675</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>7.14</v>
+        <v>18.17</v>
       </c>
       <c r="P18" s="5" t="inlineStr">
         <is>
@@ -1838,19 +1864,19 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>Otomatik MPN eşleşmesi BAT54A (çift, SOT-23) getirdi; footprint'e uyan tekli SOD-123 seçildi.</t>
+          <t>21.09 ikinci kontrolde LED kategorisi indekslendi. Renk tasarımda tanımsız; R14 2k2 ile akım ~0,6 mA olduğundan yüksek verimli kırmızı seçildi. Alternatifler: APHHS1005CGCK yeşil (190 stok, 10,63 TL), 16-213SURC/S530-A3/TR8 kırmızı (150 stok, 1,94 TL, MOQ 10, daha sönük).</t>
         </is>
       </c>
       <c r="S18" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/schottky-diyotlar-385/ons-bat54t1g-614028</t>
+          <t>https://www.ozdisan.com/p/sinyal-ledler-tek-renkli-361/kingbright-aphhs1005surck-708179</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>TH1</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1858,39 +1884,39 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>BZT52C12</t>
+          <t>10k NTC</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SOD-123</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>BZT52C12</t>
+          <t>TSM0B103F3381RZ</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>BZT52-C12_R1_00001</t>
+          <t>TSM0B103F3381RZ</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>PANJIT</t>
+          <t>THINKING</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>ZENER 410mW 12V SOD123 5%</t>
+          <t>NTC 0402 10K 1% B3380</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>560765</v>
+        <v>509291</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4720</v>
+        <v>8430</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>5</v>
@@ -1902,10 +1928,10 @@
         <v>5</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>1.11884</v>
+        <v>4.86845</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>5.59</v>
+        <v>24.34</v>
       </c>
       <c r="P19" s="5" t="inlineStr">
         <is>
@@ -1914,20 +1940,20 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Yeni seçildi</t>
+          <t>Önceden seçilmiş</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/zener-diyotlar-390/panjit-bzt52-c12-r1-00001-560765</t>
+          <t>https://www.ozdisan.com/p/ntc-termistorler-852/thinking-tsm0b103f3381rz-509291</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1935,80 +1961,54 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>22u</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>7.3x7.3x4.5</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>APHHS1005SURCK</t>
-        </is>
-      </c>
+          <t>SRI0704-220M</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>KINGBRIGHT</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>LED SMD 0402 RED 630nm 220mcd</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>708179</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>272</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>18.1675</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>Uygun</t>
+          <t>CORE MASTER</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n"/>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>Stokta yok</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Yeni seçildi</t>
+          <t>Önceden seçilmiş</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>21.09 ikinci kontrolde LED kategorisi indekslendi. Renk tasarımda tanımsız; R14 2k2 ile akım ~0,6 mA olduğundan yüksek verimli kırmızı seçildi. Alternatifler: APHHS1005CGCK yeşil (190 stok, 10,63 TL), 16-213SURC/S530-A3/TR8 kırmızı (150 stok, 1,94 TL, MOQ 10, daha sönük).</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>https://www.ozdisan.com/p/sinyal-ledler-tek-renkli-361/kingbright-aphhs1005surck-708179</t>
-        </is>
-      </c>
+          <t>11.09 raporunda Özdisan stoklu seçilmişti; bugün indekste yok (aynı serinin başka değerleri stokta). Aynı ayağa uyan 22µH stokta yok. En yakını ETQP5M220YFM (22µH 3.7A, 7.5x7 mm, 434 stok); farklı footprint.</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TH1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -2016,113 +2016,139 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10k NTC</t>
+          <t>6u8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>1210 (3225)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>TSM0B103F3381RZ</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>TSM0B103F3381RZ</t>
+          <t>B82422H1682K000</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>THINKING</t>
+          <t>EPCOS (TDK)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>NTC 0402 10K 1% B3380</t>
+          <t>INDUCTOR 1210 6.8UH SMD</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>509291</v>
+        <v>489001</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8430</v>
+        <v>10</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>4.86845</v>
+        <v>19.0045</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>24.34</v>
-      </c>
-      <c r="P21" s="5" t="inlineStr">
-        <is>
-          <t>Uygun</t>
+        <v>19</v>
+      </c>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>Uyarı</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Önceden seçilmiş</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr"/>
+          <t>Yeni seçildi</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Footprint'e uyan tek parça. TPS55340 boost bobini için 1210 çip bobinin akımı (yüzlerce mA) yetersiz; tasarımda bobin/footprint kontrolü gerekli. Stok 10.</t>
+        </is>
+      </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/ntc-termistorler-852/thinking-tsm0b103f3381rz-509291</t>
+          <t>https://www.ozdisan.com/p/sabit-induktorler-468/epcos-tdk-b82422h1682k000-489001</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>SW1,SW2</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>22u</t>
+          <t>PTS810</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7.3x7.3x4.5</t>
+          <t>PTS810 SMD</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>SRI0704-220M</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
+          <t>PTS810 SJS 250 SMTR LFS</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>PTS810 SJS 250 SMTR LFS</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>CORE MASTER</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="3" t="n"/>
-      <c r="O22" s="3" t="n"/>
-      <c r="P22" s="4" t="inlineStr">
-        <is>
-          <t>Stokta yok</t>
+          <t>C&amp;K-LITTELFUSE</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>SWITCH TACT 4.2x3.2 SMT</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>994927</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>315791</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>10.9363</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2130,17 +2156,17 @@
           <t>Önceden seçilmiş</t>
         </is>
       </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>11.09 raporunda Özdisan stoklu seçilmişti; bugün indekste yok (aynı serinin başka değerleri stokta). Aynı ayağa uyan 22µH stokta yok. En yakını ETQP5M220YFM (22µH 3.7A, 7.5x7 mm, 434 stok); farklı footprint.</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="n"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ozdisan.com/p/tact-sivicler-485/littelfuse-ck-pts810-sjs-250-smtr-lfs-994927</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>SW3</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -2148,36 +2174,58 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2u2</t>
+          <t>EC1121S enkoder</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MAPI-4030</t>
+          <t>EC1121S THT</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>74438357022</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
+          <t>L-KLS4-EC1121S-E5A-F12.5</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>L-KLS4-EC1121S-E5A-F12.5</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>WURTH</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="P23" s="4" t="inlineStr">
-        <is>
-          <t>Stokta yok</t>
+          <t>KLS ELECTRONIC</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>ENCODER 11MM WITH SWITCH</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>533942</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1013</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>31.2392</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>31.24</v>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2187,15 +2235,19 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>Özdisan'da bulunamadı. MAPI-4030 ayağına uyan 2.2µH / Isat≥2A stokta yok.</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="n"/>
+          <t>Şema sembolü/ayağı ile uyumlu olan seçildi. Ön BOM'daki L-KLS4-EC12-012424-W de stokta (93) ama footprint'e uymaz.</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ozdisan.com/p/enkoderler-532/kls-electronic-l-kls4-ec1121s-e5a-f12-5-533942</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -2203,39 +2255,39 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6u8</t>
+          <t>1F5</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1210 (3225)</t>
+          <t>Ø19 H-tipi yatay coin, P20 (CR2032 yuvası yerine)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>DCL5R5155HF</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>B82422H1682K000</t>
+          <t>DCL5R5155HF</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>EPCOS (TDK)</t>
+          <t>KORCHIP</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>INDUCTOR 1210 6.8UH SMD</t>
+          <t>CAP.SUPER 1.5F 5.5VDC 19x6.5 20mm H Type THT</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>489001</v>
+        <v>954330</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>10</v>
+        <v>289</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>1</v>
@@ -2247,14 +2299,14 @@
         <v>1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>19.0045</v>
+        <v>58.556</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="P24" s="8" t="inlineStr">
-        <is>
-          <t>Uyarı</t>
+        <v>58.56</v>
+      </c>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2264,59 +2316,59 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>Footprint'e uyan tek parça. TPS55340 boost bobini için 1210 çip bobinin akımı (yüzlerce mA) yetersiz; tasarımda bobin/footprint kontrolü gerekli. Stok 10.</t>
+          <t>21.09 RTC revizyonu: BT1 (CR2032) yerine süper kapasitör. 5,5V anma, ESR ≤30 Ω, −25…70°C. Yedek süre ≈ C·(3,3−1,4)/1,5 µA ≈ 22 gün (TCFE=1); kaçak akım bu süreyi kısaltır, prototipte ölçülmeli. Proje footprint'i: Power_Output_Custom:Korchip_DCL_H-Type_D19.0mm_P20.00mm_Horizontal (datasheet çiziminden; numune ile doğrulanmalı). Reflow'a girmez, elle lehim.</t>
         </is>
       </c>
       <c r="S24" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/sabit-induktorler-468/epcos-tdk-b82422h1682k000-489001</t>
+          <t>https://www.ozdisan.com/p/elektrik-cift-katmanli-kapasitorler-super-kapasitorler-183/korchip-dcl5r5155hf-954330</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SW1,SW2</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>PTS810</t>
+          <t>32.768kHz</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>PTS810 SMD</t>
+          <t>ABS25 4-SMD 8.0x3.8</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>PTS810 SJS 250 SMTR LFS</t>
+          <t>ABS25-32.768KHZ-T</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>PTS810 SJS 250 SMTR LFS</t>
+          <t>ABS25-32.768KHZ-T</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>C&amp;K-LITTELFUSE</t>
+          <t>ABRACON</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SWITCH TACT 4.2x3.2 SMT</t>
+          <t>CRYSTAL 32.768kHz 12.5pF 20PPM 8X4X2.5 SMD</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>994927</v>
+        <v>489027</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>315791</v>
+        <v>1534</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>1</v>
@@ -2325,13 +2377,13 @@
         <v>1</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>10.9363</v>
+        <v>18.7481</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>21.87</v>
+        <v>18.75</v>
       </c>
       <c r="P25" s="5" t="inlineStr">
         <is>
@@ -2340,20 +2392,24 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Önceden seçilmiş</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr"/>
+          <t>Yeni seçildi</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>21.09 RTC revizyonu: BQ32000 kristali: CL 12,5 pF (datasheet 10,8–13,2 pF), ESR 50 kΩ (max 70 kΩ), ±20 ppm. Pin 1–4 kristal, 2–3 bağlantısız (şemada GND). 3215 alternatifleri (RT3215, ABS07) ESR 70 kΩ ile sınırda.</t>
+        </is>
+      </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/tact-sivicler-485/littelfuse-ck-pts810-sjs-250-smtr-lfs-994927</t>
+          <t>https://www.ozdisan.com/p/kristaller-508/abracon-abs25-32-768khz-t-489027</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SW3</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -2361,22 +2417,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EC1121S enkoder</t>
+          <t>TFT032B018 FPC</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>EC1121S THT</t>
+          <t>FPC 0.5mm 30p ZIF (40p Molex'ten)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>L-KLS4-EC1121S-E5A-F12.5</t>
+          <t>L-KLS1-242I-2.0-30-R</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>L-KLS4-EC1121S-E5A-F12.5</t>
+          <t>L-KLS1-242I-2.0-30-R</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2386,14 +2442,14 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>ENCODER 11MM WITH SWITCH</t>
+          <t>CONN.FOR TFT SMT 30PIN 0.5MM FLIP TYPE</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>533942</v>
+        <v>695049</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1013</v>
+        <v>1248</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>1</v>
@@ -2405,10 +2461,10 @@
         <v>1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>31.2392</v>
+        <v>12.6162</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>31.24</v>
+        <v>12.62</v>
       </c>
       <c r="P26" s="5" t="inlineStr">
         <is>
@@ -2417,24 +2473,24 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Tasarım MPN'i</t>
+          <t>Yeni seçildi</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>Şema sembolü/ayağı ile uyumlu olan seçildi. Ön BOM'daki L-KLS4-EC12-012424-W de stokta (93) ama footprint'e uymaz.</t>
+          <t>22.09 TFT032B018 revizyonu: NHD-2.4 (40p Molex 54132-4062) yerine TFT032B018 için 30p 0,5mm çift temaslı flip ZIF. Proje footprint'i Connector_FPC_Custom:KLS_L-KLS1-242I-2.0-30_1x30-2MP_P0.50mm_Horizontal (KLS1-242I datasheet PCB layout'undan; FPC yönü numune ile doğrulanmalı).</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/enkoderler-532/kls-electronic-l-kls4-ec1121s-e5a-f12-5-533942</t>
+          <t>https://www.ozdisan.com/p/ffc-ve-fpc-konnektorler-716/kls-electronic-l-kls1-242i-2-0-30-r-695049</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -2442,39 +2498,39 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1F5</t>
+          <t>IRLML6344</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Ø19 H-tipi yatay coin, P20 (CR2032 yuvası yerine)</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>DCL5R5155HF</t>
+          <t>IRLML6344TRPBF</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>DCL5R5155HF</t>
+          <t>IRLML6344TRPBF</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>KORCHIP</t>
+          <t>INFINEON</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>CAP.SUPER 1.5F 5.5VDC 19x6.5 20mm H Type THT</t>
+          <t>MOSFET DIS.5A 30V N-CH SOT23 SMT</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>954330</v>
+        <v>612260</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>289</v>
+        <v>1274</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>1</v>
@@ -2486,10 +2542,10 @@
         <v>1</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>58.556</v>
+        <v>5.80585</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>58.56</v>
+        <v>5.81</v>
       </c>
       <c r="P27" s="5" t="inlineStr">
         <is>
@@ -2503,19 +2559,19 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>21.09 RTC revizyonu: BT1 (CR2032) yerine süper kapasitör. 5,5V anma, ESR ≤30 Ω, −25…70°C. Yedek süre ≈ C·(3,3−1,4)/1,5 µA ≈ 22 gün (TCFE=1); kaçak akım bu süreyi kısaltır, prototipte ölçülmeli. Proje footprint'i: Power_Output_Custom:Korchip_DCL_H-Type_D19.0mm_P20.00mm_Horizontal (datasheet çiziminden; numune ile doğrulanmalı). Reflow'a girmez, elle lehim.</t>
+          <t>22.09 TFT032B018 revizyonu: Backlight düşük taraf anahtarı (BL_K), TFT_BL_PWM ile R28 üzerinden sürülür. Lojik seviye; Özdisan kaydı 30V / 5A / 29 mΩ / 1,3W.</t>
         </is>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/elektrik-cift-katmanli-kapasitorler-super-kapasitorler-183/korchip-dcl5r5155hf-954330</t>
+          <t>https://www.ozdisan.com/p/discrete-mosfetler-435/infineon-irlml6344trpbf-612260</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Y1</t>
+          <t>R60</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -2523,54 +2579,54 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>32.768kHz</t>
+          <t>5R6</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ABS25 4-SMD 8.0x3.8</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>ABS25-32.768KHZ-T</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>ABS25-32.768KHZ-T</t>
+          <t>CRT05J7F5R60</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>ABRACON</t>
+          <t>VIKING</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>CRYSTAL 32.768kHz 12.5pF 20PPM 8X4X2.5 SMD</t>
+          <t>RES 0805 5.6R 5% 1/8W 100PPM</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>489027</v>
+        <v>1054409</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1534</v>
+        <v>90200</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.7481</v>
+        <v>0.07325</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>18.75</v>
+        <v>7.32</v>
       </c>
       <c r="P28" s="5" t="inlineStr">
         <is>
@@ -2584,19 +2640,19 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>21.09 RTC revizyonu: BQ32000 kristali: CL 12,5 pF (datasheet 10,8–13,2 pF), ESR 50 kΩ (max 70 kΩ), ±20 ppm. Pin 1–4 kristal, 2–3 bağlantısız (şemada GND). 3215 alternatifleri (RT3215, ABS07) ESR 70 kΩ ile sınırda.</t>
+          <t>22.09 TFT032B018 revizyonu: Backlight akım direnci, +3.3V → BL_A. I = (3,32 − VF)/5,6 ≈ 21…93 mA (VF 3,2…2,8V), tipik ~57 mA; ≤100 mA panel sınırı korunur. 93 mA'de 48 mW (1/8W). Parlaklık numune ile ölçülüp değer ayarlanabilir.</t>
         </is>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/kristaller-508/abracon-abs25-32-768khz-t-489027</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/viking-crt05j7f5r60-1054409</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>TFT (şema dışı)</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -2604,39 +2660,39 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>FPC 40p</t>
+          <t>TFT032B018</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>FPC 0.5mm 40p</t>
+          <t>3.2in IPS modül</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54132-4062</t>
+          <t>TFT032B018</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>541324062</t>
+          <t>TFT032B018</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>MOLEX</t>
+          <t>XIAMEN PRECISE</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>CONN FFC BOTTOM 40POS 0.5MM R/A</t>
+          <t>TFT PANEL 3.2" 240x320 MCU / SERIAL INTERFACE 30P</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1325143</v>
+        <v>1564112</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13297</v>
+        <v>5</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>1</v>
@@ -2648,29 +2704,29 @@
         <v>1</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>43.7858</v>
+        <v>298.662</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t>Uygun</t>
+        <v>298.66</v>
+      </c>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>Uyarı</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Tasarım MPN'i</t>
+          <t>Yeni seçildi</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>21.09 ikinci kontrolde indekste bulundu (Özdisan MPN'i tiresiz: 541324062).</t>
+          <t>22.09 TFT032B018 revizyonu: Ekran modülü (şemada sembol yok, J3'e takılır). ST7789V2, 4 telli SPI, IPS, 5 paralel LED VF 3,0V/100 mA. Stok yalnız 5 (MPQ 10): seri üretim için temin süresi sorulmalı. Parlaklık datasheet'te belirtilmemiş.</t>
         </is>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/ffc-ve-fpc-konnektorler-716/molex-541324062-1325143</t>
+          <t>https://www.ozdisan.com/p/tft-paneller-381/xiamen-precise-tft032b018-1564112</t>
         </is>
       </c>
     </row>
@@ -3000,11 +3056,11 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>C1,C2,C6,C11,C14,C17,C22,C24,C26,C32</t>
+          <t>C1,C2,C6,C11,C14,C17,C24,C26,C32</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -3162,11 +3218,11 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>C4,C7,C9</t>
+          <t>C4,C7,C9,C34</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
@@ -3231,7 +3287,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>C4 (PD_5V) için ≥10V şartını karşılar. C9: BQ32000 VCC dekuplajı, datasheet ≥1 µF istiyor (100n → 1u0).</t>
+          <t>C4 (PD_5V) için ≥10V şartını karşılar. C9: BQ32000 VCC dekuplajı, datasheet ≥1 µF istiyor (100n → 1u0). C34: TFT032B018 VCI/IOVCC dekuplajı (J3 yanında).</t>
         </is>
       </c>
       <c r="S37" s="6" t="inlineStr">
@@ -3243,11 +3299,11 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>C5,C20,C21</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -3292,13 +3348,13 @@
         <v>1</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>16.3012</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>48.9</v>
+        <v>16.3</v>
       </c>
       <c r="P38" s="5" t="inlineStr">
         <is>
@@ -3312,7 +3368,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>21.09 üçüncü tur: Footprint 0402 → 0805. 10V X6S (+105°C), 3.3V/4.2V raylarında 6.3V parçalardan daha az DC-bias kaybı; TPS61023/RT4812 çıkış efektif ≥4 µF şartını rahat karşılar. Ucuz alternatif: CL21A226MQQNNNE 6,3V X5R (47890 stok, 2,18 TL).</t>
+          <t>21.09 üçüncü tur: Footprint 0402 → 0805. 10V X6S (+105°C); ESP32 +3.3V bulk. (22.09: C20/C21 TFT032B018 revizyonunda kalktı.)</t>
         </is>
       </c>
       <c r="S38" s="6" t="inlineStr">
@@ -4736,11 +4792,11 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>R45</t>
+          <t>R21 (DNP)</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
@@ -4759,7 +4815,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>TC0250B1003TCC</t>
+          <t>CQ02WGF1003TCE</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4769,33 +4825,25 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 100K 0.1% 1/16W</t>
+          <t>RES 0402 100K 1% 1/16W AEC-Q200</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>569693</v>
+        <v>587906</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>368</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>5</v>
-      </c>
+        <v>99900</v>
+      </c>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
       <c r="N57" s="3" t="n">
-        <v>1.42196</v>
-      </c>
-      <c r="O57" s="3" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="P57" s="5" t="inlineStr">
-        <is>
-          <t>Uygun</t>
+        <v>0.04378</v>
+      </c>
+      <c r="O57" s="3" t="n"/>
+      <c r="P57" s="10" t="inlineStr">
+        <is>
+          <t>Satın alınmaz</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -4805,27 +4853,27 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>%0,1 şartı (BL_BOOST_FB bölücüsü).</t>
+          <t>DNP; dizilmez.</t>
         </is>
       </c>
       <c r="S57" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-tc0250b1003tcc-569693</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-cq02wgf1003tce-587906</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>R21 (DNP)</t>
+          <t>R51,R54</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>1k0</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4840,35 +4888,43 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>CQ02WGF1003TCE</t>
+          <t>RT0402BRD071KL</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>ROYALOHM</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 100K 1% 1/16W AEC-Q200</t>
+          <t>RES 0402 1K 0.1% 1/16W 25PPM</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>587906</v>
+        <v>1212342</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>99900</v>
-      </c>
-      <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n"/>
+        <v>37995</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="N58" s="3" t="n">
-        <v>0.04378</v>
-      </c>
-      <c r="O58" s="3" t="n"/>
-      <c r="P58" s="10" t="inlineStr">
-        <is>
-          <t>Satın alınmaz</t>
+        <v>2.54552</v>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="P58" s="5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -4878,23 +4934,23 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>DNP; dizilmez.</t>
+          <t>0402 1k %1 stokta yok; %0,1 ince film seçildi.</t>
         </is>
       </c>
       <c r="S58" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-cq02wgf1003tce-587906</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/yageo-rt0402brd071kl-1212342</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>R51,R54</t>
+          <t>R43</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
@@ -4903,7 +4959,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -4913,39 +4969,39 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>RT0402BRD071KL</t>
+          <t>PS122WF1001T4E</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>ROYALOHM</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 1K 0.1% 1/16W 25PPM</t>
+          <t>RES 2512 1K 1% 2W anti-surge</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1212342</v>
+        <v>746122</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>37995</v>
+        <v>93571</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>2.54552</v>
+        <v>5.15035</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>12.73</v>
+        <v>5.15</v>
       </c>
       <c r="P59" s="5" t="inlineStr">
         <is>
@@ -4959,19 +5015,19 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>0402 1k %1 stokta yok; %0,1 ince film seçildi.</t>
+          <t>2W şartı (28V'ta 0.651W).</t>
         </is>
       </c>
       <c r="S59" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/yageo-rt0402brd071kl-1212342</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-ps122wf1001t4e-746122</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>R43</t>
+          <t>R39</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
@@ -4979,12 +5035,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>1k0</t>
+          <t>10k2 (10k yerine)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -4994,43 +5050,43 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>PS122WF1001T4E</t>
+          <t>RC1005F1022CS</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>ROYALOHM</t>
+          <t>SAMSUNG</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>RES 2512 1K 1% 2W anti-surge</t>
+          <t>RES 0402 10.2K 1% 1/16W</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>746122</v>
+        <v>695131</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>93571</v>
+        <v>5865</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>5.15035</v>
+        <v>0.36274</v>
       </c>
       <c r="O60" s="3" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="P60" s="5" t="inlineStr">
-        <is>
-          <t>Uygun</t>
+        <v>7.25</v>
+      </c>
+      <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>Muadil</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -5040,19 +5096,19 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>2W şartı (28V'ta 0.651W).</t>
+          <t>21.09 üçüncü tur: R40 3,24k ile birlikte AOZ1284 çıkışını 3,3185V'ta tutmak için 10k → 10,2k (bkz. R40).</t>
         </is>
       </c>
       <c r="S60" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-ps122wf1001t4e-746122</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/samsung-rc1005f1022cs-695131</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>R39</t>
+          <t>R40</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
@@ -5060,7 +5116,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>10k2 (10k yerine)</t>
+          <t>3k24 (3k20 yerine)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -5075,24 +5131,24 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>RC1005F1022CS</t>
+          <t>ERJ2RKF3241X</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>SAMSUNG</t>
+          <t>PANASONIC</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 10.2K 1% 1/16W</t>
+          <t>RES 0402 3.24K 1% 1/10W</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>695131</v>
+        <v>494659</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>5865</v>
+        <v>76745</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>20</v>
@@ -5104,10 +5160,10 @@
         <v>20</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0.36274</v>
+        <v>0.3664</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>7.25</v>
+        <v>7.33</v>
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
@@ -5121,19 +5177,19 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>21.09 üçüncü tur: R40 3,24k ile birlikte AOZ1284 çıkışını 3,3185V'ta tutmak için 10k → 10,2k (bkz. R40).</t>
+          <t>21.09 üçüncü tur: AOZ1284 FB bölücüsü (R39 üst, R40 alt, VFB 0,8V). %1'de 3,2k yok → R40 = 3,24k; çıkışı korumak için R39 10k → 10,2k. VOUT = 0,8×(1+10,2/3,24) = 3,3185V (eski 3,300V; +%0,56, AOZ1284 VFB toleransı ±%1,5 içinde). R46 ile aynı MPN.</t>
         </is>
       </c>
       <c r="S61" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/samsung-rc1005f1022cs-695131</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/panasoniceurope-erj2rkf3241x-494659</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>R40</t>
+          <t>R41</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -5141,7 +5197,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>3k24 (3k20 yerine)</t>
+          <t>12k7</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5156,43 +5212,43 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>ERJ2RKF3241X</t>
+          <t>0402WGF1272TCE</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>PANASONIC</t>
+          <t>ROYALOHM</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 3.24K 1% 1/10W</t>
+          <t>RES 0402 12.7K 1% 1/16W</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>494659</v>
+        <v>506317</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>76745</v>
+        <v>18380</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>0.3664</v>
+        <v>0.02873</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="P62" s="7" t="inlineStr">
-        <is>
-          <t>Muadil</t>
+        <v>5.75</v>
+      </c>
+      <c r="P62" s="5" t="inlineStr">
+        <is>
+          <t>Uygun</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -5200,21 +5256,17 @@
           <t>Yeni seçildi</t>
         </is>
       </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>21.09 üçüncü tur: AOZ1284 FB bölücüsü (R39 üst, R40 alt, VFB 0,8V). %1'de 3,2k yok → R40 = 3,24k; çıkışı korumak için R39 10k → 10,2k. VOUT = 0,8×(1+10,2/3,24) = 3,3185V (eski 3,300V; +%0,56, AOZ1284 VFB toleransı ±%1,5 içinde). R46 ile aynı MPN.</t>
-        </is>
-      </c>
+      <c r="R62" s="2" t="inlineStr"/>
       <c r="S62" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/panasoniceurope-erj2rkf3241x-494659</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf1272tce-506317</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>R41</t>
+          <t>R47</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
@@ -5222,7 +5274,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>12k7</t>
+          <t>78k7</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -5237,7 +5289,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>0402WGF1272TCE</t>
+          <t>0402WGF7872TCE</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5247,14 +5299,14 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 12.7K 1% 1/16W</t>
+          <t>RES 0402 78.7K 1% 1/16W</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>506317</v>
+        <v>506387</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>18380</v>
+        <v>7070</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>200</v>
@@ -5284,14 +5336,14 @@
       <c r="R63" s="2" t="inlineStr"/>
       <c r="S63" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf1272tce-506317</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf7872tce-506387</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>R44</t>
+          <t>R48</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
@@ -5299,7 +5351,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>604k</t>
+          <t>30k1</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -5314,7 +5366,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>0402WGF6043TCE</t>
+          <t>0402WGF3012TCE</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -5324,14 +5376,14 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 604K 1% 1/16W</t>
+          <t>RES 0402 30.1K 1% 1/16W</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>506466</v>
+        <v>506349</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>42500</v>
+        <v>10680</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>200</v>
@@ -5358,21 +5410,17 @@
           <t>Yeni seçildi</t>
         </is>
       </c>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>21.09 üçüncü tur: %1 kabul edildi. BACKLIGHT_4V2 bölücü toleransı ~±%1,2'ye çıkar (VFB toleransı hariç); CAT4104 payına etkisi ihmal edilebilir.</t>
-        </is>
-      </c>
+      <c r="R64" s="2" t="inlineStr"/>
       <c r="S64" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf6043tce-506466</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf3012tce-506349</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>R46</t>
+          <t>R49</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
@@ -5380,7 +5428,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>3k24</t>
+          <t>9k76</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -5395,39 +5443,39 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>ERJ2RKF3241X</t>
+          <t>0402WGF9761TCE</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>PANASONIC</t>
+          <t>ROYALOHM</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 3.24K 1% 1/10W</t>
+          <t>RES 0402 9.76K 1% 1/16W</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>494659</v>
+        <v>506310</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>76745</v>
+        <v>17170</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>0.3664</v>
+        <v>0.02873</v>
       </c>
       <c r="O65" s="3" t="n">
-        <v>7.33</v>
+        <v>5.75</v>
       </c>
       <c r="P65" s="5" t="inlineStr">
         <is>
@@ -5439,21 +5487,17 @@
           <t>Yeni seçildi</t>
         </is>
       </c>
-      <c r="R65" s="2" t="inlineStr">
-        <is>
-          <t>21.09 üçüncü tur: %1 kabul edildi. CAT4104 RSET → kanal başı ~39,8 mA, direnç toleransı ±%1 akıma yaklaşık ±%1 yansır. R40 ile aynı MPN.</t>
-        </is>
-      </c>
+      <c r="R65" s="2" t="inlineStr"/>
       <c r="S65" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/panasoniceurope-erj2rkf3241x-494659</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf9761tce-506310</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>R47</t>
+          <t>R50</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
@@ -5461,7 +5505,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>78k7</t>
+          <t>820R</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -5476,39 +5520,39 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>0402WGF7872TCE</t>
+          <t>RC0402JR-07820RL</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>ROYALOHM</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 78.7K 1% 1/16W</t>
+          <t>RES 0402 820R 5% 1/16W</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>506387</v>
+        <v>423409</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7070</v>
+        <v>92000</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>0.02873</v>
+        <v>0.06567000000000001</v>
       </c>
       <c r="O66" s="3" t="n">
-        <v>5.75</v>
+        <v>6.57</v>
       </c>
       <c r="P66" s="5" t="inlineStr">
         <is>
@@ -5520,17 +5564,21 @@
           <t>Yeni seçildi</t>
         </is>
       </c>
-      <c r="R66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>0402 820R yalnız %5 stokta.</t>
+        </is>
+      </c>
       <c r="S66" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf7872tce-506387</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/yageo-rc0402jr-07820rl-423409</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>R48</t>
+          <t>R52</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
@@ -5538,7 +5586,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>30k1</t>
+          <t>2k0</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -5553,39 +5601,39 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>0402WGF3012TCE</t>
+          <t>ERJ2RKF2001X</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>ROYALOHM</t>
+          <t>PANASONIC</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 30.1K 1% 1/16W</t>
+          <t>RES 0402 2K 1% 1/10W</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>506349</v>
+        <v>518487</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>10680</v>
+        <v>34590</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0.02873</v>
+        <v>0.3664</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>5.75</v>
+        <v>7.33</v>
       </c>
       <c r="P67" s="5" t="inlineStr">
         <is>
@@ -5600,14 +5648,14 @@
       <c r="R67" s="2" t="inlineStr"/>
       <c r="S67" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf3012tce-506349</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/panasoniceurope-erj2rkf2001x-518487</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>R49</t>
+          <t>R55</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
@@ -5615,7 +5663,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>9k76</t>
+          <t>232k</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -5630,7 +5678,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>0402WGF9761TCE</t>
+          <t>0402WGF2323TCE</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -5640,14 +5688,14 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 9.76K 1% 1/16W</t>
+          <t>RES 0402 232K 1% 1/16W</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>506310</v>
+        <v>506426</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>17170</v>
+        <v>6600</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>200</v>
@@ -5677,27 +5725,27 @@
       <c r="R68" s="2" t="inlineStr"/>
       <c r="S68" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf9761tce-506310</t>
+          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf2323tce-506426</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>R50</t>
+          <t>R11,RShunt1</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>820R</t>
+          <t>5m0</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -5707,39 +5755,39 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>RC0402JR-07820RL</t>
+          <t>BVT-I-R005-1.0</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>ISABELLENHÜTTE</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>RES 0402 820R 5% 1/16W</t>
+          <t>RES.SHUNT 2512 5mΩ 1% 2.5W Isaohm AEC-Q200</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>423409</v>
+        <v>536256</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>92000</v>
+        <v>774</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>0.06567000000000001</v>
+        <v>56.1615</v>
       </c>
       <c r="O69" s="3" t="n">
-        <v>6.57</v>
+        <v>112.32</v>
       </c>
       <c r="P69" s="5" t="inlineStr">
         <is>
@@ -5753,324 +5801,88 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>0402 820R yalnız %5 stokta.</t>
+          <t>21.09 dördüncü tur: 'Hassas ve Şönt Dirençler' kategorisi indekslendi; stok 774 (+25 yolda) doğrulandı. Datasheet (BVT 2512): 6,35×3,05 mm, 5 mΩ ±%1, TCR 0±50 ppm/K, 2,5 W @70°C / 1,5 W @100°C terminal; 5 A'de kayıp 0,125 W. Footprint notu: KiCad R_2512_6332Metric mekanik olarak uyar; üretici ped önerisi farklı (toplam 7 mm, genişlik 3,4 mm, iç aralık 1,8 mm), ısı ve Kelvin ölçüm noktası için özel footprint önerilir. Alternatif: VMS-R005-1.0-U (Isabellenhütte, 2512, 3 W, TCR ±20 ppm/K, 1473 stok, 54,08 TL) — ped düzeni VMS datasheet'ine göre kontrol edilmeli.</t>
         </is>
       </c>
       <c r="S69" s="6" t="inlineStr">
         <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/yageo-rc0402jr-07820rl-423409</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>R52</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>2k0</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>ERJ2RKF2001X</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>PANASONIC</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>RES 0402 2K 1% 1/10W</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>518487</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>34590</v>
-      </c>
-      <c r="K70" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="M70" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N70" s="3" t="n">
-        <v>0.3664</v>
-      </c>
-      <c r="O70" s="3" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="P70" s="5" t="inlineStr">
-        <is>
-          <t>Uygun</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>Yeni seçildi</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="6" t="inlineStr">
-        <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/panasoniceurope-erj2rkf2001x-518487</t>
+          <t>https://www.ozdisan.com/p/hassas-ve-sont-direncler-195/isabellenhutte-bvt-i-r005-1-0-536256</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>R55</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>232k</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>0402</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>0402WGF2323TCE</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>ROYALOHM</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>RES 0402 232K 1% 1/16W</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>506426</v>
-      </c>
-      <c r="J71" s="2" t="n">
-        <v>6600</v>
-      </c>
-      <c r="K71" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="N71" s="3" t="n">
-        <v>0.02873</v>
-      </c>
-      <c r="O71" s="3" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="P71" s="5" t="inlineStr">
-        <is>
-          <t>Uygun</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>Yeni seçildi</t>
-        </is>
-      </c>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="6" t="inlineStr">
-        <is>
-          <t>https://www.ozdisan.com/p/smt-smd-ve-cip-direncler-194/royalohm-0402wgf2323tce-506426</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>R11,RShunt1</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>5m0</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>2512</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>BVT-I-R005-1.0</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>ISABELLENHÜTTE</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>RES.SHUNT 2512 5mΩ 1% 2.5W Isaohm AEC-Q200</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>536256</v>
-      </c>
-      <c r="J72" s="2" t="n">
-        <v>774</v>
-      </c>
-      <c r="K72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N72" s="3" t="n">
-        <v>56.1615</v>
-      </c>
-      <c r="O72" s="3" t="n">
-        <v>112.32</v>
-      </c>
-      <c r="P72" s="5" t="inlineStr">
-        <is>
-          <t>Uygun</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>Yeni seçildi</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>21.09 dördüncü tur: 'Hassas ve Şönt Dirençler' kategorisi indekslendi; stok 774 (+25 yolda) doğrulandı. Datasheet (BVT 2512): 6,35×3,05 mm, 5 mΩ ±%1, TCR 0±50 ppm/K, 2,5 W @70°C / 1,5 W @100°C terminal; 5 A'de kayıp 0,125 W. Footprint notu: KiCad R_2512_6332Metric mekanik olarak uyar; üretici ped önerisi farklı (toplam 7 mm, genişlik 3,4 mm, iç aralık 1,8 mm), ısı ve Kelvin ölçüm noktası için özel footprint önerilir. Alternatif: VMS-R005-1.0-U (Isabellenhütte, 2512, 3 W, TCR ±20 ppm/K, 1473 stok, 54,08 TL) — ped düzeni VMS datasheet'ine göre kontrol edilmeli.</t>
-        </is>
-      </c>
-      <c r="S72" s="6" t="inlineStr">
-        <is>
-          <t>https://www.ozdisan.com/p/hassas-ve-sont-direncler-195/isabellenhutte-bvt-i-r005-1-0-536256</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="11" t="inlineStr">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>TOPLAM (fiyatı bulunan satırlar)</t>
         </is>
       </c>
-      <c r="O74" s="12">
-        <f>SUM(O2:O72)</f>
+      <c r="O71" s="12">
+        <f>SUM(O2:O69)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S72"/>
+  <autoFilter ref="A1:S69"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S19" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S69" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S70" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S71" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S72" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S25" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S27" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S28" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S29" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S30" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S35" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S36" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S37" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S42" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S44" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S45" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S46" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S47" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S48" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S49" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S50" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S51" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S52" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S53" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S54" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S55" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S56" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S57" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S58" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S59" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S60" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S61" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S62" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S63" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S64" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S65" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S66" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S67" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S68" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S69" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6082,7 +5894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -6240,7 +6052,7 @@
         </is>
       </c>
       <c r="B9" s="20">
-        <f>SUM(BOM_Ozdisan!O2:O72)</f>
+        <f>SUM(BOM_Ozdisan!O2:O69)</f>
         <v/>
       </c>
     </row>
@@ -6268,19 +6080,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21.09 RTC revizyonu: RV-3028-C7 + CR2032 → BQ32000DR + 1,5F süper kapasitör (C33) + kristal Y1; BT1, R22, R23, C10 kaldırıldı, C9 1u0 oldu.</t>
+          <t>22.09 TFT032B018 revizyonu: NHD-2.4 + TPS61023 boost + CAT4104 → TFT032B018 (3,2" IPS, ST7789V2) + KLS 30p FPC + Q7/R60 PWM backlight; U7, U8, L2, C20, C21, C22, R44, R45, R46 kaldırıldı.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21.09 üçüncü tur: U2/U4/U7/J7 muadil kontrolü, C3/C5/C8/C15/C19/C20/C21/C25/C27/C28/C29/C31 ve R39/R40/R44/R46/R59/R11/RShunt1 yeniden seçildi. Footprint veya değer değişikliği gerektiren satırlar Not sütununda belirtildi; şema değiştirilmedi.</t>
+          <t>21.09 RTC revizyonu: RV-3028-C7 + CR2032 → BQ32000DR + 1,5F süper kapasitör (C33) + kristal Y1; BT1, R22, R23, C10 kaldırıldı, C9 1u0 oldu.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>21.09 üçüncü tur: U2/U4/U7/J7 muadil kontrolü, C3/C5/C8/C15/C19/C20/C21/C25/C27/C28/C29/C31 ve R39/R40/R44/R46/R59/R11/RShunt1 yeniden seçildi. Footprint veya değer değişikliği gerektiren satırlar Not sütununda belirtildi; şema değiştirilmedi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>21.09 ikinci kontrol: pil tutucu, FFC/FPC, PCB klemens, LED ve Wi-Fi modül kategorileri indekse eklendi. Hâlâ indekslenmemiş: USB konnektörler (J7) ve binding post (J5, J6); bu satırlar Özdisan'a ayrıca sorulmalı.</t>
         </is>
